--- a/sinodalias.xlsx
+++ b/sinodalias.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ildeberto/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ildeberto/Desktop/Recopilacion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5D0882F-2968-9049-90BA-77117272F338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB8EE9C9-DFAD-6440-B2B2-504CD0CA7B64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="36000" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,14 +20,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="156">
   <si>
     <t>FUNCIÓN</t>
   </si>
   <si>
-    <t>SUSTENTANTE</t>
-  </si>
-  <si>
     <t>FECHA</t>
   </si>
   <si>
@@ -40,9 +37,6 @@
     <t>TEMA</t>
   </si>
   <si>
-    <t>FUENTE(S)</t>
-  </si>
-  <si>
     <t>PRESIDENTE</t>
   </si>
   <si>
@@ -55,18 +49,12 @@
     <t>EXAMEN GLOBAL POR ÁREAS DEL CONOCIMIENTO</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 2; jurado2.xlsx fila 61</t>
-  </si>
-  <si>
     <t>VOCAL PROPIETARIO</t>
   </si>
   <si>
     <t>ALEJANDRA DEL SOCORRO VERA GOMEZ</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 3; jurado2.xlsx fila 48</t>
-  </si>
-  <si>
     <t>ALEJANDRO CRUZ RODRIGUEZ</t>
   </si>
   <si>
@@ -76,9 +64,6 @@
     <t>DISEÑO DE UN SISTEMA ELECTRÓNICO DE MEDICIÓN MEDIANTE TELEMETRÍA DE LAS PRINCIPALES VARIABLES DE OPERACIÓN EN UN COCHE TIPO ELECTRATRON (V, I, T) USANDO UNA CELDA DE COMBUSTIBLE DE 2 KW COMO SISTEMA DE PROPULSIÓN</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 4</t>
-  </si>
-  <si>
     <t>ALVARO RODRIGUEZ VAZQUEZ</t>
   </si>
   <si>
@@ -88,9 +73,6 @@
     <t>SISTEMA DE CONTROL DE INTENSIDAD LUMINOSA EN HABITACIÓN</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 5; jurado2.xlsx fila 34</t>
-  </si>
-  <si>
     <t>SECRETARIO</t>
   </si>
   <si>
@@ -100,18 +82,12 @@
     <t>CONTROL DE VELOCIDAD DE UN MOTOR DE CD UTILIZADO EN UNA BANDA TRANSPORTADORA</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 6</t>
-  </si>
-  <si>
     <t>ANGEL JAVIER AGUILAR ARANDA</t>
   </si>
   <si>
     <t>MÓDULO COMUNICACIONES</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 7</t>
-  </si>
-  <si>
     <t>VOCAL SUPLENTE</t>
   </si>
   <si>
@@ -124,102 +100,57 @@
     <t>IMPLEMENTACIÓN DE UN SISTEMA DE REFLECTANCIA PARA MONITOREAR LOS NIVELES DE CARGADO DE PARTÍCULAS DE DIAMANTES EN DISCO DE Sn</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 8</t>
-  </si>
-  <si>
     <t>ARTEMIO DE JESUS CASTILLO COELLO</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 9; jurado2.xlsx fila 42</t>
-  </si>
-  <si>
     <t>BRUNO AVILA BALBOA</t>
   </si>
   <si>
     <t>MÓDULO II: DIGITALES</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 10</t>
-  </si>
-  <si>
     <t>CARLOS ALBERTO CASTRO MATAMOROS</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 11; jurado2.xlsx fila 24</t>
-  </si>
-  <si>
     <t>CARLOS ALBERTO DOMINGUEZ VELAZQUEZ</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 12</t>
-  </si>
-  <si>
     <t>CARLOS ALBERTO GUTIERREZ DAVILA</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 13</t>
-  </si>
-  <si>
     <t>CARLOS ENRIQUE MENDEZ PADILLA</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 14; jurado2.xlsx fila 39</t>
-  </si>
-  <si>
     <t>CARLOS MARTIN MUNGUIA BALLINAS</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 15</t>
-  </si>
-  <si>
     <t>CLAUDIA DE JESUS AGUILAR NAVARRO</t>
   </si>
   <si>
     <t>SIMULACIÓN CON MATLAB DE UN CONTROLADOR DIFUSO PARA UN PÉNDULO INVERTIDO</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 16</t>
-  </si>
-  <si>
     <t>DANIEL TOVAR GUILLEN</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 17; jurado2.xlsx fila 47</t>
-  </si>
-  <si>
     <t>DAVID FERNANDO ARGUMEDO CASTAÑON</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 18; jurado2.xlsx fila 64</t>
-  </si>
-  <si>
     <t>EDDANY OCHOA ZAVALA</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 19</t>
-  </si>
-  <si>
     <t>EDGAR ORTIZ LOPEZ</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 20</t>
-  </si>
-  <si>
     <t>EDMUNDO DE JESUS CORONADO COUTIÑO</t>
   </si>
   <si>
     <t>EXAMEN GENERAL PARA EL EGRESO DE LA LICENCIATURA EN INGENIERÍA ELECTRÓNICA</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 21</t>
-  </si>
-  <si>
     <t>EDRAS GOMEZ SOLIS</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 22</t>
-  </si>
-  <si>
     <t>EDUARDO CHANDOMI CASTELLANOS</t>
   </si>
   <si>
@@ -229,102 +160,57 @@
     <t>TESIS</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 23; jurado2.xlsx fila 11</t>
-  </si>
-  <si>
     <t>ELVIA ALEJANDRA MORENO MATUZ</t>
   </si>
   <si>
     <t>SINCRONIZACIÓN Y CONTROL DE CAOS Y SUS APLICACIONES POTENCIALES</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 24</t>
-  </si>
-  <si>
     <t>ENRIQUE ALONSO MENDEZ JIMENEZ</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 25; jurado2.xlsx fila 62</t>
-  </si>
-  <si>
     <t>ENRIQUE ANTONIO MARTINEZ GORDILLO</t>
   </si>
   <si>
     <t>CONTROL DIFUSO DE VELOCIDAD DE UN MOTOR DE INDUCCIÓN CA CON TARJETA DE ADQUISICIÓN DE DATOS</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 26</t>
-  </si>
-  <si>
     <t>ERIKA IVETTE SOSA CHANONA</t>
   </si>
   <si>
     <t>CONTROL DE TEMPERATURA DE UN INVERNADERO PARA LA PRODUCCIÓN DE ORQUÍDEAS</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 27</t>
-  </si>
-  <si>
     <t>EUGENIO LOPEZ DIAZ</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 28; jurado2.xlsx fila 57</t>
-  </si>
-  <si>
     <t>FERNANDO FLORES BOLAÑOS</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 29; jurado2.xlsx fila 54</t>
-  </si>
-  <si>
     <t>FERNANDO RAFAEL MARTINEZ ALGARIN</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 30; jurado2.xlsx fila 2</t>
-  </si>
-  <si>
     <t>FRANCISCO JAVIER PEREZ DIAZ</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 31</t>
-  </si>
-  <si>
     <t>GERMAN IVAN HERNANDEZ GOMEZ</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 32; jurado2.xlsx fila 59</t>
-  </si>
-  <si>
     <t>GUTEMBER PEREZ TAMS</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 33</t>
-  </si>
-  <si>
     <t>HAROLDO DIAZ SANCHEZ</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 34; jurado2.xlsx fila 65</t>
-  </si>
-  <si>
     <t>HELEN DARIAS HERNANDEZ</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 35; jurado2.xlsx fila 9</t>
-  </si>
-  <si>
     <t>HIRAM CAMACHO COELLO</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 36; jurado2.xlsx fila 44</t>
-  </si>
-  <si>
     <t>HUGO HUMBERTO TORRES VENTURA</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 37</t>
-  </si>
-  <si>
     <t>HUNBERTO GOMES VELASQUES</t>
   </si>
   <si>
@@ -334,84 +220,51 @@
     <t>CÁMARA MÓVIL DE ALETARGAMIENTO DE MOSCAS ESTÉRILES</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 38; jurado2.xlsx fila 23</t>
-  </si>
-  <si>
     <t>IGNACIO HERNANDEZ HERNANDEZ</t>
   </si>
   <si>
     <t>SIMULACIÓN DE UN SISTEMA DE CONTROL DIFUSO CON MATLAB</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 39</t>
-  </si>
-  <si>
     <t>IRVING LORENZANO ELVIRA</t>
   </si>
   <si>
     <t>ESCOLARIDAD POR PROMEDIO</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 40; jurado2.xlsx fila 55</t>
-  </si>
-  <si>
     <t>ISABEL ALEGRIA DE LOS SANTOS</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 41; jurado2.xlsx fila 20</t>
-  </si>
-  <si>
     <t>IVAN MARTIN SANTIZ DOMINGUEZ</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 42</t>
-  </si>
-  <si>
     <t>JESUS RAYMUNDO BARRANCO ZARAZUA</t>
   </si>
   <si>
     <t>TESIS PROFESIONAL</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 43; jurado2.xlsx fila 53</t>
-  </si>
-  <si>
     <t>JORGE DAVID SANTIZ VARGAS</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 44</t>
-  </si>
-  <si>
     <t>JORGE ENRIQUE SESMA GUTIERREZ</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 45; jurado2.xlsx fila 32</t>
-  </si>
-  <si>
     <t>JOSE ANOC DIAZ HERRERA</t>
   </si>
   <si>
     <t>MÓDULO I: ELECTRÓNICA</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 46</t>
-  </si>
-  <si>
     <t>JOSE ANTONIO BORRAZ SANCHEZ</t>
   </si>
   <si>
     <t>CONTROL DE TEMPERATURA DE UN CALENTADOR DE AGUA RESIDENCIAL</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 47; jurado2.xlsx fila 33</t>
-  </si>
-  <si>
     <t>JOSE ANTONIO CLEMENTE MANUEL</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 48</t>
-  </si>
-  <si>
     <t>JOSE BRUNO ROBLERO GALDAMEZ</t>
   </si>
   <si>
@@ -421,405 +274,210 @@
     <t>PROCESADORES DIGITALES DE SEÑALES</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 49</t>
-  </si>
-  <si>
     <t>JOSE FIDEL URBINA SALINAS</t>
   </si>
   <si>
     <t>ESCOLARIDAD POR ESTUDIOS DE POSGRADO</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 50; jurado2.xlsx fila 43</t>
-  </si>
-  <si>
     <t>JOSE ILLNES TRUJILLO LOPEZ</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 51; jurado2.xlsx fila 46</t>
-  </si>
-  <si>
     <t>JOSE LUIS GOMEZ ORANTES</t>
   </si>
   <si>
     <t>SIMULACIÓN CON MATLAB DE UN SISTEMA VIGA Y BOLA (BALANCIN)</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 52</t>
-  </si>
-  <si>
     <t>JOSEFA GORDILLO ESTRADA</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 53</t>
-  </si>
-  <si>
     <t>JUAN CARLOS LOPEZ MORENO</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 54</t>
-  </si>
-  <si>
     <t>JUAN CARLOS SALINAS HERNANDEZ</t>
   </si>
   <si>
     <t>RECONOCIMIENTO AUTOMÁTICO DE FORMAS CON DESCRIPTORES DE FOURIER</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 55; jurado2.xlsx fila 17</t>
-  </si>
-  <si>
     <t>JUAN ESTEBAN MOTA CRUZ</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 56; jurado2.xlsx fila 31</t>
-  </si>
-  <si>
     <t>JUAN MANUEL HERNANDEZ PEREZ</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 57</t>
-  </si>
-  <si>
     <t>JULIO ALBERTO GUZMAN RABASA</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 58; jurado2.xlsx fila 16</t>
-  </si>
-  <si>
     <t>JULIO CESAR GOMEZ MENDEZ</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 59; jurado2.xlsx fila 40</t>
-  </si>
-  <si>
     <t>JULIO CESAR MARTINEZ MORGAN</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 60; jurado2.xlsx fila 10</t>
-  </si>
-  <si>
     <t>JULIO CESAR SIERRA OCAÑA</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 61; jurado2.xlsx fila 58</t>
-  </si>
-  <si>
     <t>JULIO CESAR VALENCIA ESCOBAR</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 62</t>
-  </si>
-  <si>
     <t>KARINA DEL ROSARIO MATUS ESPINOSA</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 63; jurado2.xlsx fila 37</t>
-  </si>
-  <si>
     <t>KARLA ALEJANDRA RIOS BAUTISTA</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 64</t>
-  </si>
-  <si>
     <t>LADY ROBIN TOALA MORENO</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 65; jurado2.xlsx fila 36</t>
-  </si>
-  <si>
     <t>VOCAL</t>
   </si>
   <si>
     <t>LEONARDO GOMEZ CORONEL</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 66; jurado2.xlsx fila 8</t>
-  </si>
-  <si>
     <t>LIMBER DE JESUS GUMETA SANTIAGO</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 67; jurado2.xlsx fila 28</t>
-  </si>
-  <si>
     <t>LORENA FAJARDO GONZALEZ</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 68</t>
-  </si>
-  <si>
     <t>LUIS ADAN SANCHEZ MEJIA</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 69; jurado2.xlsx fila 5</t>
-  </si>
-  <si>
     <t>LUIS IVAN MORENO GOMEZ</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 70; jurado2.xlsx fila 29</t>
-  </si>
-  <si>
     <t>MADAI VELASCO SANCHEZ</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 71; jurado2.xlsx fila 18</t>
-  </si>
-  <si>
     <t>MANUEL ALBERTO BRINDIS SANCHEZ</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 72; jurado2.xlsx fila 19</t>
-  </si>
-  <si>
     <t>MANUEL NUCAMENDI SERRANO</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 73; jurado2.xlsx fila 21</t>
-  </si>
-  <si>
     <t>MARCO ANTONIO CASTILLO SOLIS</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 74</t>
-  </si>
-  <si>
     <t>MARCO ANTONIO PACHECO TOVAR</t>
   </si>
   <si>
     <t>CONTROL DE TEMPERATURA DE UNA DESHIDRATADORA DE MANGO CON LÓGICA DIFUSA</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 75; jurado2.xlsx fila 30</t>
-  </si>
-  <si>
     <t>MARIA DEL ROCIO COELLO VILA</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 76; jurado2.xlsx fila 50</t>
-  </si>
-  <si>
     <t>MARIA ELOISA AGUILAR FIGUEROA</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 77; jurado2.xlsx fila 26</t>
-  </si>
-  <si>
     <t>MARIA ISCIS ESCOBAR ESCOBAR</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 78</t>
-  </si>
-  <si>
     <t>MARYA JOHARA MARQUEZ ZEPEDA</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 79; jurado2.xlsx fila 7</t>
-  </si>
-  <si>
     <t>MAURICIO SOLIS IBARRA</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 80; jurado2.xlsx fila 63</t>
-  </si>
-  <si>
     <t>MIGUEL ANGEL AGUILAR CUESTA</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 81; jurado2.xlsx fila 51</t>
-  </si>
-  <si>
     <t>MIGUEL ANGEL MENDEZ ALTUZAR</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 82; jurado2.xlsx fila 49</t>
-  </si>
-  <si>
     <t>MOCTEZUMA VICTORIA VELAZQUEZ</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 83; jurado2.xlsx fila 60</t>
-  </si>
-  <si>
     <t>NATALIA TRUJILLO SANCHEZ</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 84; jurado2.xlsx fila 22</t>
-  </si>
-  <si>
     <t>NOE ABADIA ESPINOSA</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 85</t>
-  </si>
-  <si>
     <t>NOEL DE JESUS AGUILAR CHON</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 86</t>
-  </si>
-  <si>
     <t>NOEL JOSIAS BELLO CRUZ</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 87</t>
-  </si>
-  <si>
     <t>NORMA CAROLINA MELENDEZ MARTINEZ</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 88</t>
-  </si>
-  <si>
     <t>PABLO GABRIEL ALVAREZ</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 89; jurado2.xlsx fila 56</t>
-  </si>
-  <si>
     <t>RAMON ARMANDO NAJERA COURTOIS</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 90; jurado2.xlsx fila 6</t>
-  </si>
-  <si>
-    <t>jurado1.xlsx fila 91</t>
-  </si>
-  <si>
     <t>RICARDO LEON DE LA CRUZ</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 92; jurado2.xlsx fila 38</t>
-  </si>
-  <si>
     <t>ROBERTO CANDIDO CRUZ NUCAMENDI</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 93</t>
-  </si>
-  <si>
     <t>RUBEN RODRIGUEZ CHAVEZ</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 94; jurado2.xlsx fila 27</t>
-  </si>
-  <si>
     <t>RUSVEL ALVAREZ SALINAS</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 95</t>
-  </si>
-  <si>
     <t>SERGIO IVAN GOMEZ CASILLAS</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 96</t>
-  </si>
-  <si>
     <t>SERGIO ROBERTO AGUILAR GOMEZ</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 97</t>
-  </si>
-  <si>
     <t>VERONICA TORRES MONTES</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 98</t>
-  </si>
-  <si>
     <t>VICENTE LOPEZ TOLEDO</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 99; jurado2.xlsx fila 45</t>
-  </si>
-  <si>
     <t>VICTOR ANTONIO CABRERA</t>
   </si>
   <si>
     <t>SIMULACIÓN CON BUILDER DE UN CONTROLADOR DIFUSO PARA UN PÉNDULO INVERTIDO</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 100</t>
-  </si>
-  <si>
     <t>VILLAREAL WONG ANUAR</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 101</t>
-  </si>
-  <si>
     <t>VIRGILIO RICARDO LAZARO ZERMEÑO</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 102; jurado2.xlsx fila 41</t>
-  </si>
-  <si>
     <t>WILDER SANCHEZ CACACHO</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 103</t>
-  </si>
-  <si>
     <t>XAVIER MOLINA GONZALEZ</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 104</t>
-  </si>
-  <si>
     <t>YASMANI GONZALEZ CARDENAS</t>
   </si>
   <si>
-    <t>jurado1.xlsx fila 105; jurado2.xlsx fila 4</t>
-  </si>
-  <si>
     <t>PEDRO GASGA GARCIA</t>
   </si>
   <si>
     <t>DOCTORADO EN CIENCIAS DE LA INGENIERÍA</t>
   </si>
   <si>
-    <t>jurado2.xlsx fila 3</t>
-  </si>
-  <si>
     <t>JESUS CABRERA GARCIA</t>
   </si>
   <si>
-    <t>jurado2.xlsx fila 12</t>
-  </si>
-  <si>
     <t>ALEJANDRO ALVARADO ALGARIN</t>
   </si>
   <si>
-    <t>jurado2.xlsx fila 13</t>
-  </si>
-  <si>
     <t>JOSE FRANCISCO MOLINA SANTIAGO</t>
   </si>
   <si>
-    <t>jurado2.xlsx fila 14</t>
-  </si>
-  <si>
     <t>VICTOR DAVID CASTILLO GONZALEZ</t>
   </si>
   <si>
-    <t>jurado2.xlsx fila 15</t>
-  </si>
-  <si>
     <t>ANUAR VILLAREAL WONG</t>
   </si>
   <si>
-    <t>jurado2.xlsx fila 25</t>
-  </si>
-  <si>
-    <t>jurado2.xlsx fila 35</t>
-  </si>
-  <si>
-    <t>jurado2.xlsx fila 52</t>
-  </si>
-  <si>
     <t>IMPLEMENTACIÓN DE UN SISTEMA EXPERTO DIFUSO PARA CONTROL DE TEMPERATURA EN AMBIENTE LINUX</t>
   </si>
   <si>
@@ -827,6 +485,9 @@
   </si>
   <si>
     <t>RENE FERNANDO MUÑOZ CASTELLANOS</t>
+  </si>
+  <si>
+    <t>NOMBRE DEL SUSTENTANTE</t>
   </si>
 </sst>
 </file>
@@ -867,13 +528,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1041,7 +701,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H113"/>
+  <dimension ref="A1:G113"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
@@ -1050,2295 +710,1955 @@
     <col min="4" max="4" width="25" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="52" customWidth="1"/>
-    <col min="7" max="7" width="62" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="16">
+    <row r="1" spans="1:7" ht="16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
       </c>
       <c r="C2" s="2">
         <v>38637</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
         <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
       </c>
       <c r="C3" s="2">
         <v>38804</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C4" s="2">
         <v>39412</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C5" s="2">
         <v>39190</v>
       </c>
       <c r="D5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" s="4"/>
-    </row>
-    <row r="6" spans="1:8">
+        <v>16</v>
+      </c>
+      <c r="G5" s="3"/>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C6" s="2">
         <v>39190</v>
       </c>
       <c r="D6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="3"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
         <v>20</v>
-      </c>
-      <c r="F6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H6" s="4"/>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" t="s">
-        <v>27</v>
       </c>
       <c r="C7" s="2">
         <v>39027</v>
       </c>
       <c r="D7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C8" s="2">
         <v>39398</v>
       </c>
       <c r="D8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C9" s="2">
         <v>38897</v>
       </c>
       <c r="D9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C10" s="2">
         <v>40844</v>
       </c>
       <c r="D10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>38</v>
-      </c>
-      <c r="G10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="C11" s="2">
         <v>39574</v>
       </c>
       <c r="D11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
         <v>30</v>
-      </c>
-      <c r="B12" t="s">
-        <v>42</v>
       </c>
       <c r="C12" s="2">
         <v>39029</v>
       </c>
       <c r="D12" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="C13" s="2">
         <v>40084</v>
       </c>
       <c r="D13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G13" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="C14" s="2">
         <v>39106</v>
       </c>
       <c r="D14" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>28</v>
-      </c>
-      <c r="G14" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="C15" s="2">
         <v>39510</v>
       </c>
       <c r="D15" t="s">
-        <v>9</v>
-      </c>
-      <c r="G15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="C16" s="2">
         <v>39514</v>
       </c>
       <c r="D16" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E16" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F16" t="s">
-        <v>51</v>
-      </c>
-      <c r="G16" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C17" s="2">
         <v>38862</v>
       </c>
       <c r="D17" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="C18" s="2">
         <v>38628</v>
       </c>
       <c r="D18" t="s">
-        <v>9</v>
-      </c>
-      <c r="G18" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="C19" s="2">
         <v>39510</v>
       </c>
       <c r="D19" t="s">
-        <v>9</v>
-      </c>
-      <c r="G19" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="C20" s="2">
         <v>40527</v>
       </c>
       <c r="D20" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="G20" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="C21" s="2">
         <v>40527</v>
       </c>
       <c r="D21" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E21" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>62</v>
-      </c>
-      <c r="G21" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="C22" s="2">
         <v>40844</v>
       </c>
       <c r="D22" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="G22" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B23" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="C23" s="2">
         <v>42916</v>
       </c>
       <c r="D23" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="E23" t="s">
-        <v>68</v>
-      </c>
-      <c r="G23" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B24" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="C24" s="2">
         <v>40060</v>
       </c>
       <c r="D24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E24" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F24" t="s">
-        <v>71</v>
-      </c>
-      <c r="G24" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="C25" s="2">
         <v>38637</v>
       </c>
       <c r="D25" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E25" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>28</v>
-      </c>
-      <c r="G25" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B26" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="C26" s="2">
         <v>39513</v>
       </c>
       <c r="D26" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E26" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F26" t="s">
-        <v>76</v>
-      </c>
-      <c r="G26" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B27" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="C27" s="2">
         <v>39167</v>
       </c>
       <c r="D27" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E27" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F27" t="s">
-        <v>79</v>
-      </c>
-      <c r="G27" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="C28" s="2">
         <v>38639</v>
       </c>
       <c r="D28" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E28" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>28</v>
-      </c>
-      <c r="G28" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B29" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="C29" s="2">
         <v>38639</v>
       </c>
       <c r="D29" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E29" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F29" t="s">
-        <v>266</v>
-      </c>
-      <c r="G29" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B30" t="s">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="C30" s="2">
         <v>46077</v>
       </c>
       <c r="D30" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="E30" t="s">
-        <v>68</v>
-      </c>
-      <c r="G30" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B31" t="s">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="C31" s="2">
         <v>40844</v>
       </c>
       <c r="D31" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E31" t="s">
-        <v>10</v>
-      </c>
-      <c r="G31" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B32" t="s">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="C32" s="2">
         <v>38638</v>
       </c>
       <c r="D32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E32" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>28</v>
-      </c>
-      <c r="G32" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="C33" s="2">
         <v>40695</v>
       </c>
       <c r="D33" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G33" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B34" t="s">
-        <v>93</v>
+        <v>59</v>
       </c>
       <c r="C34" s="2">
         <v>38628</v>
       </c>
       <c r="D34" t="s">
-        <v>9</v>
-      </c>
-      <c r="G34" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B35" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="C35" s="2">
         <v>44742</v>
       </c>
       <c r="D35" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="E35" t="s">
-        <v>68</v>
-      </c>
-      <c r="G35" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B36" t="s">
-        <v>97</v>
+        <v>61</v>
       </c>
       <c r="C36" s="2">
         <v>38863</v>
       </c>
       <c r="D36" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E36" t="s">
-        <v>10</v>
-      </c>
-      <c r="G36" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B37" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="C37" s="2">
         <v>40085</v>
       </c>
       <c r="D37" t="s">
-        <v>9</v>
-      </c>
-      <c r="G37" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B38" t="s">
-        <v>101</v>
+        <v>63</v>
       </c>
       <c r="C38" s="2">
         <v>39577</v>
       </c>
       <c r="D38" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E38" t="s">
-        <v>102</v>
+        <v>64</v>
       </c>
       <c r="F38" t="s">
-        <v>103</v>
-      </c>
-      <c r="G38" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B39" t="s">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="C39" s="2">
         <v>39169</v>
       </c>
       <c r="D39" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E39" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F39" t="s">
-        <v>106</v>
-      </c>
-      <c r="G39" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B40" t="s">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="C40" s="2">
         <v>38639</v>
       </c>
       <c r="D40" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E40" t="s">
-        <v>109</v>
-      </c>
-      <c r="G40" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B41" t="s">
-        <v>111</v>
+        <v>70</v>
       </c>
       <c r="C41" s="2">
         <v>40491</v>
       </c>
       <c r="D41" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E41" t="s">
-        <v>10</v>
-      </c>
-      <c r="G41" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B42" t="s">
-        <v>113</v>
+        <v>71</v>
       </c>
       <c r="C42" s="2">
         <v>38981</v>
       </c>
       <c r="D42" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E42" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F42" t="s">
-        <v>28</v>
-      </c>
-      <c r="G42" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B43" t="s">
-        <v>115</v>
+        <v>72</v>
       </c>
       <c r="C43" s="2">
         <v>38643</v>
       </c>
       <c r="D43" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E43" t="s">
-        <v>116</v>
-      </c>
-      <c r="G43" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B44" t="s">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="C44" s="2">
         <v>39167</v>
       </c>
       <c r="D44" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E44" t="s">
-        <v>20</v>
-      </c>
-      <c r="G44" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B45" t="s">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="C45" s="2">
         <v>39191</v>
       </c>
       <c r="D45" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E45" t="s">
-        <v>20</v>
-      </c>
-      <c r="G45" t="s">
-        <v>121</v>
-      </c>
-      <c r="H45" s="4"/>
-    </row>
-    <row r="46" spans="1:8">
+        <v>15</v>
+      </c>
+      <c r="G45" s="3"/>
+    </row>
+    <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B46" t="s">
-        <v>122</v>
+        <v>76</v>
       </c>
       <c r="C46" s="2">
         <v>40084</v>
       </c>
       <c r="D46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E46" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F46" t="s">
-        <v>123</v>
-      </c>
-      <c r="G46" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B47" t="s">
-        <v>125</v>
+        <v>78</v>
       </c>
       <c r="C47" s="2">
         <v>39190</v>
       </c>
       <c r="D47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E47" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F47" t="s">
-        <v>126</v>
-      </c>
-      <c r="G47" t="s">
-        <v>127</v>
-      </c>
-      <c r="H47" s="4"/>
-    </row>
-    <row r="48" spans="1:8">
+        <v>79</v>
+      </c>
+      <c r="G47" s="3"/>
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B48" t="s">
-        <v>128</v>
+        <v>80</v>
       </c>
       <c r="C48" s="2">
         <v>39168</v>
       </c>
       <c r="D48" t="s">
-        <v>9</v>
-      </c>
-      <c r="G48" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B49" t="s">
-        <v>130</v>
+        <v>81</v>
       </c>
       <c r="C49" s="2">
         <v>39394</v>
       </c>
       <c r="D49" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E49" t="s">
-        <v>131</v>
+        <v>82</v>
       </c>
       <c r="F49" t="s">
-        <v>132</v>
-      </c>
-      <c r="G49" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B50" t="s">
-        <v>134</v>
+        <v>84</v>
       </c>
       <c r="C50" s="2">
         <v>38875</v>
       </c>
       <c r="D50" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E50" t="s">
-        <v>135</v>
-      </c>
-      <c r="G50" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B51" t="s">
-        <v>137</v>
+        <v>86</v>
       </c>
       <c r="C51" s="2">
         <v>38863</v>
       </c>
       <c r="D51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E51" t="s">
-        <v>10</v>
-      </c>
-      <c r="G51" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B52" t="s">
-        <v>139</v>
+        <v>87</v>
       </c>
       <c r="C52" s="2">
         <v>39512</v>
       </c>
       <c r="D52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E52" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F52" t="s">
-        <v>140</v>
-      </c>
-      <c r="G52" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B53" t="s">
-        <v>142</v>
+        <v>89</v>
       </c>
       <c r="C53" s="2">
         <v>40060</v>
       </c>
       <c r="D53" t="s">
-        <v>9</v>
-      </c>
-      <c r="G53" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B54" t="s">
-        <v>144</v>
+        <v>90</v>
       </c>
       <c r="C54" s="2">
         <v>40063</v>
       </c>
       <c r="D54" t="s">
-        <v>9</v>
-      </c>
-      <c r="G54" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B55" t="s">
-        <v>146</v>
+        <v>91</v>
       </c>
       <c r="C55" s="2">
         <v>40681</v>
       </c>
       <c r="D55" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E55" t="s">
-        <v>116</v>
+        <v>73</v>
       </c>
       <c r="F55" t="s">
-        <v>147</v>
-      </c>
-      <c r="G55" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B56" t="s">
-        <v>149</v>
+        <v>93</v>
       </c>
       <c r="C56" s="2">
         <v>39192</v>
       </c>
       <c r="D56" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E56" t="s">
-        <v>20</v>
-      </c>
-      <c r="G56" t="s">
-        <v>150</v>
-      </c>
-      <c r="H56" s="4"/>
-    </row>
-    <row r="57" spans="1:8">
+        <v>15</v>
+      </c>
+      <c r="G56" s="3"/>
+    </row>
+    <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B57" t="s">
-        <v>151</v>
+        <v>94</v>
       </c>
       <c r="C57" s="2">
         <v>39027</v>
       </c>
       <c r="D57" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E57" t="s">
-        <v>10</v>
-      </c>
-      <c r="G57" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B58" t="s">
-        <v>153</v>
+        <v>95</v>
       </c>
       <c r="C58" s="2">
         <v>42915</v>
       </c>
       <c r="D58" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="E58" t="s">
-        <v>68</v>
-      </c>
-      <c r="G58" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B59" t="s">
-        <v>155</v>
+        <v>96</v>
       </c>
       <c r="C59" s="2">
         <v>39106</v>
       </c>
       <c r="D59" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E59" t="s">
-        <v>32</v>
-      </c>
-      <c r="G59" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B60" t="s">
-        <v>157</v>
+        <v>97</v>
       </c>
       <c r="C60" s="2">
         <v>44734</v>
       </c>
       <c r="D60" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="E60" t="s">
-        <v>68</v>
-      </c>
-      <c r="G60" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B61" t="s">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="C61" s="2">
         <v>38639</v>
       </c>
       <c r="D61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E61" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F61" t="s">
-        <v>28</v>
-      </c>
-      <c r="G61" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B62" t="s">
-        <v>161</v>
+        <v>99</v>
       </c>
       <c r="C62" s="2">
         <v>40527</v>
       </c>
       <c r="D62" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E62" t="s">
-        <v>10</v>
-      </c>
-      <c r="G62" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B63" t="s">
-        <v>163</v>
-      </c>
-      <c r="C63" s="3">
+        <v>100</v>
+      </c>
+      <c r="C63" s="2">
         <v>39107</v>
       </c>
       <c r="D63" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E63" t="s">
-        <v>10</v>
-      </c>
-      <c r="G63" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B64" t="s">
-        <v>165</v>
+        <v>101</v>
       </c>
       <c r="C64" s="2">
         <v>40085</v>
       </c>
       <c r="D64" t="s">
-        <v>9</v>
-      </c>
-      <c r="G64" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
       <c r="A65" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B65" t="s">
-        <v>167</v>
+        <v>102</v>
       </c>
       <c r="C65" s="2">
         <v>39108</v>
       </c>
       <c r="D65" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E65" t="s">
-        <v>32</v>
-      </c>
-      <c r="G65" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
       <c r="A66" t="s">
-        <v>169</v>
+        <v>103</v>
       </c>
       <c r="B66" t="s">
-        <v>170</v>
+        <v>104</v>
       </c>
       <c r="C66" s="2">
         <v>45145</v>
       </c>
       <c r="D66" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="E66" t="s">
-        <v>68</v>
-      </c>
-      <c r="G66" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
       <c r="A67" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B67" t="s">
-        <v>172</v>
+        <v>105</v>
       </c>
       <c r="C67" s="2">
         <v>39328</v>
       </c>
       <c r="D67" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E67" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F67" t="s">
-        <v>38</v>
-      </c>
-      <c r="G67" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
       <c r="A68" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B68" t="s">
-        <v>174</v>
+        <v>106</v>
       </c>
       <c r="C68" s="2">
         <v>39132</v>
       </c>
       <c r="D68" t="s">
-        <v>9</v>
-      </c>
-      <c r="G68" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
       <c r="A69" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B69" t="s">
-        <v>176</v>
+        <v>107</v>
       </c>
       <c r="C69" s="2">
         <v>45806</v>
       </c>
       <c r="D69" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="E69" t="s">
-        <v>68</v>
-      </c>
-      <c r="G69" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
       <c r="A70" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B70" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="C70" s="2">
         <v>39192</v>
       </c>
       <c r="D70" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E70" t="s">
-        <v>20</v>
-      </c>
-      <c r="G70" t="s">
-        <v>179</v>
-      </c>
-      <c r="H70" s="4"/>
-    </row>
-    <row r="71" spans="1:8">
+        <v>15</v>
+      </c>
+      <c r="G70" s="3"/>
+    </row>
+    <row r="71" spans="1:7">
       <c r="A71" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B71" t="s">
-        <v>180</v>
+        <v>109</v>
       </c>
       <c r="C71" s="2">
         <v>40491</v>
       </c>
       <c r="D71" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E71" t="s">
-        <v>10</v>
-      </c>
-      <c r="G71" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
       <c r="A72" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B72" t="s">
-        <v>182</v>
+        <v>110</v>
       </c>
       <c r="C72" s="2">
         <v>40491</v>
       </c>
       <c r="D72" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E72" t="s">
-        <v>10</v>
-      </c>
-      <c r="G72" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
       <c r="A73" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B73" t="s">
-        <v>184</v>
+        <v>111</v>
       </c>
       <c r="C73" s="2">
         <v>40491</v>
       </c>
       <c r="D73" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E73" t="s">
-        <v>10</v>
-      </c>
-      <c r="G73" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
       <c r="A74" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B74" t="s">
-        <v>186</v>
+        <v>112</v>
       </c>
       <c r="C74" s="2">
         <v>39391</v>
       </c>
       <c r="D74" t="s">
-        <v>9</v>
-      </c>
-      <c r="G74" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
       <c r="A75" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B75" t="s">
-        <v>188</v>
+        <v>113</v>
       </c>
       <c r="C75" s="2">
         <v>39192</v>
       </c>
       <c r="D75" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E75" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F75" t="s">
-        <v>189</v>
-      </c>
-      <c r="G75" t="s">
-        <v>190</v>
-      </c>
-      <c r="H75" s="4"/>
-    </row>
-    <row r="76" spans="1:8">
+        <v>114</v>
+      </c>
+      <c r="G75" s="3"/>
+    </row>
+    <row r="76" spans="1:7">
       <c r="A76" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B76" t="s">
-        <v>191</v>
+        <v>115</v>
       </c>
       <c r="C76" s="2">
         <v>38775</v>
       </c>
       <c r="D76" t="s">
-        <v>9</v>
-      </c>
-      <c r="G76" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
       <c r="A77" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B77" t="s">
-        <v>193</v>
+        <v>116</v>
       </c>
       <c r="C77" s="2">
         <v>39353</v>
       </c>
       <c r="D77" t="s">
-        <v>9</v>
-      </c>
-      <c r="G77" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
       <c r="A78" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B78" t="s">
-        <v>195</v>
+        <v>117</v>
       </c>
       <c r="C78" s="2">
         <v>39412</v>
       </c>
       <c r="D78" t="s">
-        <v>9</v>
-      </c>
-      <c r="G78" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
       <c r="A79" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B79" t="s">
-        <v>197</v>
+        <v>118</v>
       </c>
       <c r="C79" s="2">
         <v>45204</v>
       </c>
       <c r="D79" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="E79" t="s">
-        <v>68</v>
-      </c>
-      <c r="G79" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
       <c r="A80" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B80" t="s">
-        <v>199</v>
+        <v>119</v>
       </c>
       <c r="C80" s="2">
         <v>38635</v>
       </c>
       <c r="D80" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E80" t="s">
-        <v>131</v>
+        <v>82</v>
       </c>
       <c r="F80" t="s">
-        <v>267</v>
-      </c>
-      <c r="G80" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
       <c r="A81" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B81" t="s">
-        <v>201</v>
+        <v>120</v>
       </c>
       <c r="C81" s="2">
         <v>38775</v>
       </c>
       <c r="D81" t="s">
-        <v>9</v>
-      </c>
-      <c r="G81" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
       <c r="A82" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B82" t="s">
-        <v>203</v>
+        <v>121</v>
       </c>
       <c r="C82" s="2">
         <v>38775</v>
       </c>
       <c r="D82" t="s">
-        <v>9</v>
-      </c>
-      <c r="G82" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
       <c r="A83" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B83" t="s">
-        <v>205</v>
+        <v>122</v>
       </c>
       <c r="C83" s="2">
         <v>38638</v>
       </c>
       <c r="D83" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E83" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F83" t="s">
-        <v>28</v>
-      </c>
-      <c r="G83" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
       <c r="A84" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B84" t="s">
-        <v>207</v>
+        <v>123</v>
       </c>
       <c r="C84" s="2">
         <v>40491</v>
       </c>
       <c r="D84" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E84" t="s">
-        <v>10</v>
-      </c>
-      <c r="G84" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
       <c r="A85" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B85" t="s">
-        <v>209</v>
+        <v>124</v>
       </c>
       <c r="C85" s="2">
         <v>40084</v>
       </c>
       <c r="D85" t="s">
-        <v>9</v>
-      </c>
-      <c r="G85" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
       <c r="A86" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B86" t="s">
-        <v>211</v>
+        <v>125</v>
       </c>
       <c r="C86" s="2">
         <v>40844</v>
       </c>
       <c r="D86" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E86" t="s">
-        <v>10</v>
-      </c>
-      <c r="G86" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
       <c r="A87" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B87" t="s">
-        <v>213</v>
+        <v>126</v>
       </c>
       <c r="C87" s="2">
         <v>40458</v>
       </c>
       <c r="D87" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E87" t="s">
-        <v>10</v>
-      </c>
-      <c r="G87" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6">
       <c r="A88" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B88" t="s">
-        <v>215</v>
+        <v>127</v>
       </c>
       <c r="C88" s="2">
         <v>40085</v>
       </c>
       <c r="D88" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E88" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F88" t="s">
-        <v>123</v>
-      </c>
-      <c r="G88" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6">
       <c r="A89" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B89" t="s">
-        <v>217</v>
+        <v>128</v>
       </c>
       <c r="C89" s="2">
         <v>38639</v>
       </c>
       <c r="D89" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E89" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F89" t="s">
-        <v>28</v>
-      </c>
-      <c r="G89" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6">
       <c r="A90" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B90" t="s">
-        <v>219</v>
+        <v>129</v>
       </c>
       <c r="C90" s="2">
         <v>45553</v>
       </c>
       <c r="D90" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="E90" t="s">
-        <v>68</v>
-      </c>
-      <c r="G90" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6">
       <c r="A91" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B91" t="s">
-        <v>268</v>
+        <v>154</v>
       </c>
       <c r="C91" s="2">
         <v>39724</v>
       </c>
       <c r="D91" t="s">
-        <v>9</v>
-      </c>
-      <c r="G91" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6">
       <c r="A92" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B92" t="s">
-        <v>222</v>
+        <v>130</v>
       </c>
       <c r="C92" s="2">
         <v>39107</v>
       </c>
       <c r="D92" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E92" t="s">
-        <v>32</v>
-      </c>
-      <c r="G92" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
       <c r="A93" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B93" t="s">
-        <v>224</v>
+        <v>131</v>
       </c>
       <c r="C93" s="2">
         <v>40458</v>
       </c>
       <c r="D93" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E93" t="s">
-        <v>10</v>
-      </c>
-      <c r="G93" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6">
       <c r="A94" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B94" t="s">
-        <v>226</v>
+        <v>132</v>
       </c>
       <c r="C94" s="2">
         <v>39331</v>
       </c>
       <c r="D94" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E94" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F94" t="s">
-        <v>38</v>
-      </c>
-      <c r="G94" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
       <c r="A95" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B95" t="s">
-        <v>228</v>
+        <v>133</v>
       </c>
       <c r="C95" s="2">
         <v>38686</v>
       </c>
       <c r="D95" t="s">
-        <v>9</v>
-      </c>
-      <c r="G95" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6">
       <c r="A96" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B96" t="s">
-        <v>230</v>
+        <v>134</v>
       </c>
       <c r="C96" s="2">
         <v>39167</v>
       </c>
       <c r="D96" t="s">
-        <v>9</v>
-      </c>
-      <c r="G96" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6">
       <c r="A97" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B97" t="s">
-        <v>232</v>
+        <v>135</v>
       </c>
       <c r="C97" s="2">
         <v>39412</v>
       </c>
       <c r="D97" t="s">
-        <v>9</v>
-      </c>
-      <c r="G97" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
       <c r="A98" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B98" t="s">
-        <v>234</v>
+        <v>136</v>
       </c>
       <c r="C98" s="2">
         <v>40063</v>
       </c>
       <c r="D98" t="s">
-        <v>9</v>
-      </c>
-      <c r="G98" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6">
       <c r="A99" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B99" t="s">
-        <v>236</v>
+        <v>137</v>
       </c>
       <c r="C99" s="2">
         <v>38863</v>
       </c>
       <c r="D99" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E99" t="s">
-        <v>10</v>
-      </c>
-      <c r="G99" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
       <c r="A100" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B100" t="s">
-        <v>238</v>
+        <v>138</v>
       </c>
       <c r="C100" s="2">
         <v>39513</v>
       </c>
       <c r="D100" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E100" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F100" t="s">
-        <v>239</v>
-      </c>
-      <c r="G100" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6">
       <c r="A101" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B101" t="s">
-        <v>241</v>
+        <v>140</v>
       </c>
       <c r="C101" s="2">
         <v>39398</v>
       </c>
       <c r="D101" t="s">
-        <v>9</v>
-      </c>
-      <c r="G101" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6">
       <c r="A102" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B102" t="s">
-        <v>243</v>
+        <v>141</v>
       </c>
       <c r="C102" s="2">
         <v>39106</v>
       </c>
       <c r="D102" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E102" t="s">
-        <v>131</v>
-      </c>
-      <c r="G102" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6">
       <c r="A103" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B103" t="s">
-        <v>245</v>
+        <v>142</v>
       </c>
       <c r="C103" s="2">
         <v>40063</v>
       </c>
       <c r="D103" t="s">
-        <v>9</v>
-      </c>
-      <c r="G103" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6">
       <c r="A104" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B104" t="s">
-        <v>247</v>
+        <v>143</v>
       </c>
       <c r="C104" s="2">
         <v>40220</v>
       </c>
       <c r="D104" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E104" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F104" t="s">
-        <v>38</v>
-      </c>
-      <c r="G104" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6">
       <c r="A105" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B105" t="s">
-        <v>249</v>
+        <v>144</v>
       </c>
       <c r="C105" s="2">
         <v>45931</v>
       </c>
       <c r="D105" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="E105" t="s">
-        <v>68</v>
-      </c>
-      <c r="G105" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6">
       <c r="A106" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B106" t="s">
-        <v>251</v>
+        <v>145</v>
       </c>
       <c r="C106" s="2">
         <v>46057</v>
       </c>
       <c r="D106" t="s">
-        <v>252</v>
+        <v>146</v>
       </c>
       <c r="E106" t="s">
-        <v>68</v>
-      </c>
-      <c r="G106" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6">
       <c r="A107" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B107" t="s">
-        <v>254</v>
+        <v>147</v>
       </c>
       <c r="C107" s="2">
         <v>45687</v>
       </c>
       <c r="D107" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="E107" t="s">
-        <v>68</v>
-      </c>
-      <c r="G107" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6">
       <c r="A108" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B108" t="s">
-        <v>256</v>
+        <v>148</v>
       </c>
       <c r="C108" s="2">
         <v>45167</v>
       </c>
       <c r="D108" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="E108" t="s">
-        <v>68</v>
-      </c>
-      <c r="G108" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
       <c r="A109" t="s">
-        <v>169</v>
+        <v>103</v>
       </c>
       <c r="B109" t="s">
-        <v>258</v>
+        <v>149</v>
       </c>
       <c r="C109" s="2">
         <v>45523</v>
       </c>
       <c r="D109" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="E109" t="s">
-        <v>68</v>
-      </c>
-      <c r="G109" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6">
       <c r="A110" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B110" t="s">
-        <v>260</v>
+        <v>150</v>
       </c>
       <c r="C110" s="2">
         <v>45523</v>
       </c>
       <c r="D110" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="E110" t="s">
-        <v>68</v>
-      </c>
-      <c r="G110" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
       <c r="A111" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B111" t="s">
-        <v>262</v>
+        <v>151</v>
       </c>
       <c r="C111" s="2">
         <v>39363</v>
       </c>
       <c r="D111" t="s">
-        <v>9</v>
-      </c>
-      <c r="G111" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6">
       <c r="A112" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B112" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C112" s="2">
         <v>39244</v>
       </c>
       <c r="D112" t="s">
-        <v>9</v>
-      </c>
-      <c r="G112" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>169</v>
+        <v>103</v>
       </c>
       <c r="B113" t="s">
-        <v>228</v>
+        <v>133</v>
       </c>
       <c r="C113" s="2">
         <v>38686</v>
       </c>
       <c r="D113" t="s">
-        <v>9</v>
-      </c>
-      <c r="G113" t="s">
-        <v>265</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/sinodalias.xlsx
+++ b/sinodalias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ildeberto/Desktop/Recopilacion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB8EE9C9-DFAD-6440-B2B2-504CD0CA7B64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ADD584C-8F6B-694E-8DDD-612934F84CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="36000" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -508,12 +508,18 @@
       <name val="Carlito"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -528,13 +534,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -770,52 +778,49 @@
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="2">
-        <v>39412</v>
-      </c>
-      <c r="D4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
+      <c r="A4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C4" s="5">
+        <v>45167</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C5" s="2">
-        <v>39190</v>
+        <v>39412</v>
       </c>
       <c r="D5" t="s">
         <v>7</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C6" s="2">
         <v>39190</v>
@@ -827,7 +832,7 @@
         <v>15</v>
       </c>
       <c r="F6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G6" s="3"/>
     </row>
@@ -836,39 +841,33 @@
         <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C7" s="2">
-        <v>39027</v>
+        <v>39190</v>
       </c>
       <c r="D7" t="s">
         <v>7</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C8" s="2">
-        <v>39398</v>
+        <v>39244</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
-      </c>
-      <c r="E8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -876,61 +875,64 @@
         <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C9" s="2">
-        <v>38897</v>
+        <v>39027</v>
       </c>
       <c r="D9" t="s">
         <v>7</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>151</v>
       </c>
       <c r="C10" s="2">
-        <v>40844</v>
+        <v>39363</v>
       </c>
       <c r="D10" t="s">
         <v>7</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C11" s="2">
-        <v>39574</v>
+        <v>39398</v>
       </c>
       <c r="D11" t="s">
         <v>7</v>
+      </c>
+      <c r="E11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C12" s="2">
-        <v>39029</v>
+        <v>38897</v>
       </c>
       <c r="D12" t="s">
         <v>7</v>
@@ -944,13 +946,19 @@
         <v>5</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C13" s="2">
-        <v>40084</v>
+        <v>40844</v>
       </c>
       <c r="D13" t="s">
         <v>7</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -958,33 +966,30 @@
         <v>5</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C14" s="2">
-        <v>39106</v>
+        <v>39574</v>
       </c>
       <c r="D14" t="s">
         <v>7</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C15" s="2">
-        <v>39510</v>
+        <v>39029</v>
       </c>
       <c r="D15" t="s">
         <v>7</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -992,36 +997,33 @@
         <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C16" s="2">
-        <v>39514</v>
+        <v>40084</v>
       </c>
       <c r="D16" t="s">
         <v>7</v>
-      </c>
-      <c r="E16" t="s">
-        <v>15</v>
-      </c>
-      <c r="F16" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C17" s="2">
-        <v>38862</v>
+        <v>39106</v>
       </c>
       <c r="D17" t="s">
         <v>7</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1029,10 +1031,10 @@
         <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C18" s="2">
-        <v>38628</v>
+        <v>39510</v>
       </c>
       <c r="D18" t="s">
         <v>7</v>
@@ -1040,27 +1042,33 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C19" s="2">
-        <v>39510</v>
+        <v>39514</v>
       </c>
       <c r="D19" t="s">
         <v>7</v>
+      </c>
+      <c r="E19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F19" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C20" s="2">
-        <v>40527</v>
+        <v>38862</v>
       </c>
       <c r="D20" t="s">
         <v>7</v>
@@ -1071,96 +1079,84 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C21" s="2">
-        <v>40527</v>
+        <v>38628</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C22" s="2">
-        <v>40844</v>
+        <v>39510</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C23" s="2">
-        <v>42916</v>
+        <v>40527</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="E23" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C24" s="2">
-        <v>40060</v>
+        <v>40527</v>
       </c>
       <c r="D24" t="s">
         <v>7</v>
       </c>
       <c r="E24" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C25" s="2">
-        <v>38637</v>
+        <v>40844</v>
       </c>
       <c r="D25" t="s">
         <v>7</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1168,39 +1164,36 @@
         <v>9</v>
       </c>
       <c r="B26" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C26" s="2">
-        <v>39513</v>
+        <v>42916</v>
       </c>
       <c r="D26" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E26" t="s">
-        <v>15</v>
-      </c>
-      <c r="F26" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B27" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C27" s="2">
-        <v>39167</v>
+        <v>40060</v>
       </c>
       <c r="D27" t="s">
         <v>7</v>
       </c>
       <c r="E27" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F27" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -1208,10 +1201,10 @@
         <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C28" s="2">
-        <v>38639</v>
+        <v>38637</v>
       </c>
       <c r="D28" t="s">
         <v>7</v>
@@ -1225,13 +1218,13 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B29" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C29" s="2">
-        <v>38639</v>
+        <v>39513</v>
       </c>
       <c r="D29" t="s">
         <v>7</v>
@@ -1240,7 +1233,7 @@
         <v>15</v>
       </c>
       <c r="F29" t="s">
-        <v>152</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -1248,33 +1241,39 @@
         <v>9</v>
       </c>
       <c r="B30" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C30" s="2">
-        <v>46077</v>
+        <v>39167</v>
       </c>
       <c r="D30" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="E30" t="s">
-        <v>45</v>
+        <v>15</v>
+      </c>
+      <c r="F30" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C31" s="2">
-        <v>40844</v>
+        <v>38639</v>
       </c>
       <c r="D31" t="s">
         <v>7</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
+      </c>
+      <c r="F31" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -1282,36 +1281,36 @@
         <v>5</v>
       </c>
       <c r="B32" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C32" s="2">
-        <v>38638</v>
+        <v>38639</v>
       </c>
       <c r="D32" t="s">
         <v>7</v>
       </c>
       <c r="E32" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F32" t="s">
-        <v>21</v>
+        <v>152</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B33" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C33" s="2">
-        <v>40695</v>
+        <v>46077</v>
       </c>
       <c r="D33" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E33" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1319,41 +1318,47 @@
         <v>5</v>
       </c>
       <c r="B34" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C34" s="2">
-        <v>38628</v>
+        <v>40844</v>
       </c>
       <c r="D34" t="s">
         <v>7</v>
+      </c>
+      <c r="E34" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B35" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C35" s="2">
-        <v>44742</v>
+        <v>38638</v>
       </c>
       <c r="D35" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="E35" t="s">
-        <v>45</v>
+        <v>8</v>
+      </c>
+      <c r="F35" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C36" s="2">
-        <v>38863</v>
+        <v>40695</v>
       </c>
       <c r="D36" t="s">
         <v>7</v>
@@ -1367,10 +1372,10 @@
         <v>5</v>
       </c>
       <c r="B37" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C37" s="2">
-        <v>40085</v>
+        <v>38628</v>
       </c>
       <c r="D37" t="s">
         <v>7</v>
@@ -1378,42 +1383,36 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="B38" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C38" s="2">
-        <v>39577</v>
+        <v>44742</v>
       </c>
       <c r="D38" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E38" t="s">
-        <v>64</v>
-      </c>
-      <c r="F38" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B39" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C39" s="2">
-        <v>39169</v>
+        <v>38863</v>
       </c>
       <c r="D39" t="s">
         <v>7</v>
       </c>
       <c r="E39" t="s">
-        <v>15</v>
-      </c>
-      <c r="F39" t="s">
-        <v>67</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1421,53 +1420,53 @@
         <v>5</v>
       </c>
       <c r="B40" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C40" s="2">
-        <v>38639</v>
+        <v>40085</v>
       </c>
       <c r="D40" t="s">
         <v>7</v>
-      </c>
-      <c r="E40" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B41" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C41" s="2">
-        <v>40491</v>
+        <v>39577</v>
       </c>
       <c r="D41" t="s">
         <v>7</v>
       </c>
       <c r="E41" t="s">
-        <v>8</v>
+        <v>64</v>
+      </c>
+      <c r="F41" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B42" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C42" s="2">
-        <v>38981</v>
+        <v>39169</v>
       </c>
       <c r="D42" t="s">
         <v>7</v>
       </c>
       <c r="E42" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F42" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1475,16 +1474,16 @@
         <v>5</v>
       </c>
       <c r="B43" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C43" s="2">
-        <v>38643</v>
+        <v>38639</v>
       </c>
       <c r="D43" t="s">
         <v>7</v>
       </c>
       <c r="E43" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1492,143 +1491,146 @@
         <v>9</v>
       </c>
       <c r="B44" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C44" s="2">
-        <v>39167</v>
+        <v>40491</v>
       </c>
       <c r="D44" t="s">
         <v>7</v>
       </c>
       <c r="E44" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B45" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C45" s="2">
-        <v>39191</v>
+        <v>38981</v>
       </c>
       <c r="D45" t="s">
         <v>7</v>
       </c>
       <c r="E45" t="s">
-        <v>15</v>
+        <v>8</v>
+      </c>
+      <c r="F45" t="s">
+        <v>21</v>
       </c>
       <c r="G45" s="3"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" t="s">
-        <v>9</v>
-      </c>
-      <c r="B46" t="s">
-        <v>76</v>
-      </c>
-      <c r="C46" s="2">
-        <v>40084</v>
-      </c>
-      <c r="D46" t="s">
-        <v>7</v>
-      </c>
-      <c r="E46" t="s">
-        <v>8</v>
-      </c>
-      <c r="F46" t="s">
-        <v>77</v>
+      <c r="A46" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C46" s="5">
+        <v>45687</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B47" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C47" s="2">
-        <v>39190</v>
+        <v>38643</v>
       </c>
       <c r="D47" t="s">
         <v>7</v>
       </c>
       <c r="E47" t="s">
-        <v>15</v>
-      </c>
-      <c r="F47" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="G47" s="3"/>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B48" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C48" s="2">
-        <v>39168</v>
+        <v>39167</v>
       </c>
       <c r="D48" t="s">
         <v>7</v>
+      </c>
+      <c r="E48" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B49" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C49" s="2">
-        <v>39394</v>
+        <v>39191</v>
       </c>
       <c r="D49" t="s">
         <v>7</v>
       </c>
       <c r="E49" t="s">
-        <v>82</v>
-      </c>
-      <c r="F49" t="s">
-        <v>83</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B50" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C50" s="2">
-        <v>38875</v>
+        <v>40084</v>
       </c>
       <c r="D50" t="s">
         <v>7</v>
       </c>
       <c r="E50" t="s">
-        <v>85</v>
+        <v>8</v>
+      </c>
+      <c r="F50" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B51" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C51" s="2">
-        <v>38863</v>
+        <v>39190</v>
       </c>
       <c r="D51" t="s">
         <v>7</v>
       </c>
       <c r="E51" t="s">
-        <v>8</v>
+        <v>15</v>
+      </c>
+      <c r="F51" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1636,184 +1638,181 @@
         <v>5</v>
       </c>
       <c r="B52" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C52" s="2">
-        <v>39512</v>
+        <v>39168</v>
       </c>
       <c r="D52" t="s">
         <v>7</v>
-      </c>
-      <c r="E52" t="s">
-        <v>15</v>
-      </c>
-      <c r="F52" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B53" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C53" s="2">
-        <v>40060</v>
+        <v>39394</v>
       </c>
       <c r="D53" t="s">
         <v>7</v>
+      </c>
+      <c r="E53" t="s">
+        <v>82</v>
+      </c>
+      <c r="F53" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B54" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C54" s="2">
-        <v>40063</v>
+        <v>38875</v>
       </c>
       <c r="D54" t="s">
         <v>7</v>
       </c>
+      <c r="E54" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" t="s">
-        <v>9</v>
-      </c>
-      <c r="B55" t="s">
-        <v>91</v>
-      </c>
-      <c r="C55" s="2">
-        <v>40681</v>
-      </c>
-      <c r="D55" t="s">
-        <v>7</v>
-      </c>
-      <c r="E55" t="s">
-        <v>73</v>
-      </c>
-      <c r="F55" t="s">
-        <v>92</v>
+      <c r="A55" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C55" s="5">
+        <v>45523</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B56" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C56" s="2">
-        <v>39192</v>
+        <v>38863</v>
       </c>
       <c r="D56" t="s">
         <v>7</v>
       </c>
       <c r="E56" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G56" s="3"/>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B57" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C57" s="2">
-        <v>39027</v>
+        <v>39512</v>
       </c>
       <c r="D57" t="s">
         <v>7</v>
       </c>
       <c r="E57" t="s">
-        <v>8</v>
+        <v>15</v>
+      </c>
+      <c r="F57" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B58" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C58" s="2">
-        <v>42915</v>
+        <v>40060</v>
       </c>
       <c r="D58" t="s">
-        <v>44</v>
-      </c>
-      <c r="E58" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B59" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C59" s="2">
-        <v>39106</v>
+        <v>40063</v>
       </c>
       <c r="D59" t="s">
         <v>7</v>
-      </c>
-      <c r="E59" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B60" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C60" s="2">
-        <v>44734</v>
+        <v>40681</v>
       </c>
       <c r="D60" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="E60" t="s">
-        <v>45</v>
+        <v>73</v>
+      </c>
+      <c r="F60" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B61" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C61" s="2">
-        <v>38639</v>
+        <v>39192</v>
       </c>
       <c r="D61" t="s">
         <v>7</v>
       </c>
       <c r="E61" t="s">
-        <v>8</v>
-      </c>
-      <c r="F61" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B62" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C62" s="2">
-        <v>40527</v>
+        <v>39027</v>
       </c>
       <c r="D62" t="s">
         <v>7</v>
@@ -1824,67 +1823,73 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B63" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C63" s="2">
-        <v>39107</v>
+        <v>42915</v>
       </c>
       <c r="D63" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E63" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B64" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C64" s="2">
-        <v>40085</v>
+        <v>39106</v>
       </c>
       <c r="D64" t="s">
         <v>7</v>
+      </c>
+      <c r="E64" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B65" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C65" s="2">
-        <v>39108</v>
+        <v>44734</v>
       </c>
       <c r="D65" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E65" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" t="s">
-        <v>103</v>
+        <v>9</v>
       </c>
       <c r="B66" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C66" s="2">
-        <v>45145</v>
+        <v>38639</v>
       </c>
       <c r="D66" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="E66" t="s">
-        <v>45</v>
+        <v>8</v>
+      </c>
+      <c r="F66" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1892,141 +1897,141 @@
         <v>17</v>
       </c>
       <c r="B67" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C67" s="2">
-        <v>39328</v>
+        <v>40527</v>
       </c>
       <c r="D67" t="s">
         <v>7</v>
       </c>
       <c r="E67" t="s">
         <v>8</v>
-      </c>
-      <c r="F67" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B68" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C68" s="2">
-        <v>39132</v>
+        <v>39107</v>
       </c>
       <c r="D68" t="s">
         <v>7</v>
+      </c>
+      <c r="E68" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B69" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C69" s="2">
-        <v>45806</v>
+        <v>40085</v>
       </c>
       <c r="D69" t="s">
-        <v>44</v>
-      </c>
-      <c r="E69" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70" spans="1:7">
       <c r="A70" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B70" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C70" s="2">
-        <v>39192</v>
+        <v>39108</v>
       </c>
       <c r="D70" t="s">
         <v>7</v>
       </c>
       <c r="E70" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G70" s="3"/>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" t="s">
-        <v>5</v>
+        <v>103</v>
       </c>
       <c r="B71" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C71" s="2">
-        <v>40491</v>
+        <v>45145</v>
       </c>
       <c r="D71" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E71" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B72" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C72" s="2">
-        <v>40491</v>
+        <v>39328</v>
       </c>
       <c r="D72" t="s">
         <v>7</v>
       </c>
       <c r="E72" t="s">
         <v>8</v>
+      </c>
+      <c r="F72" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B73" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C73" s="2">
-        <v>40491</v>
+        <v>39132</v>
       </c>
       <c r="D73" t="s">
         <v>7</v>
-      </c>
-      <c r="E73" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B74" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C74" s="2">
-        <v>39391</v>
+        <v>45806</v>
       </c>
       <c r="D74" t="s">
-        <v>7</v>
+        <v>44</v>
+      </c>
+      <c r="E74" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B75" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C75" s="2">
         <v>39192</v>
@@ -2037,37 +2042,40 @@
       <c r="E75" t="s">
         <v>15</v>
       </c>
-      <c r="F75" t="s">
-        <v>114</v>
-      </c>
       <c r="G75" s="3"/>
     </row>
     <row r="76" spans="1:7">
       <c r="A76" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B76" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C76" s="2">
-        <v>38775</v>
+        <v>40491</v>
       </c>
       <c r="D76" t="s">
         <v>7</v>
+      </c>
+      <c r="E76" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="77" spans="1:7">
       <c r="A77" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B77" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C77" s="2">
-        <v>39353</v>
+        <v>40491</v>
       </c>
       <c r="D77" t="s">
         <v>7</v>
+      </c>
+      <c r="E77" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2075,30 +2083,30 @@
         <v>9</v>
       </c>
       <c r="B78" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C78" s="2">
-        <v>39412</v>
+        <v>40491</v>
       </c>
       <c r="D78" t="s">
         <v>7</v>
+      </c>
+      <c r="E78" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B79" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C79" s="2">
-        <v>45204</v>
+        <v>39391</v>
       </c>
       <c r="D79" t="s">
-        <v>44</v>
-      </c>
-      <c r="E79" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2106,27 +2114,27 @@
         <v>17</v>
       </c>
       <c r="B80" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C80" s="2">
-        <v>38635</v>
+        <v>39192</v>
       </c>
       <c r="D80" t="s">
         <v>7</v>
       </c>
       <c r="E80" t="s">
-        <v>82</v>
+        <v>15</v>
       </c>
       <c r="F80" t="s">
-        <v>153</v>
+        <v>114</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B81" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C81" s="2">
         <v>38775</v>
@@ -2137,13 +2145,13 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B82" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C82" s="2">
-        <v>38775</v>
+        <v>39353</v>
       </c>
       <c r="D82" t="s">
         <v>7</v>
@@ -2151,22 +2159,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B83" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C83" s="2">
-        <v>38638</v>
+        <v>39412</v>
       </c>
       <c r="D83" t="s">
         <v>7</v>
-      </c>
-      <c r="E83" t="s">
-        <v>8</v>
-      </c>
-      <c r="F83" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -2174,16 +2176,16 @@
         <v>9</v>
       </c>
       <c r="B84" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C84" s="2">
-        <v>40491</v>
+        <v>45204</v>
       </c>
       <c r="D84" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="E84" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -2191,58 +2193,58 @@
         <v>17</v>
       </c>
       <c r="B85" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C85" s="2">
-        <v>40084</v>
+        <v>38635</v>
       </c>
       <c r="D85" t="s">
         <v>7</v>
+      </c>
+      <c r="E85" t="s">
+        <v>82</v>
+      </c>
+      <c r="F85" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="86" spans="1:6">
       <c r="A86" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B86" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C86" s="2">
-        <v>40844</v>
+        <v>38775</v>
       </c>
       <c r="D86" t="s">
         <v>7</v>
-      </c>
-      <c r="E86" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="A87" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B87" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C87" s="2">
-        <v>40458</v>
+        <v>38775</v>
       </c>
       <c r="D87" t="s">
         <v>7</v>
-      </c>
-      <c r="E87" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="88" spans="1:6">
       <c r="A88" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B88" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C88" s="2">
-        <v>40085</v>
+        <v>38638</v>
       </c>
       <c r="D88" t="s">
         <v>7</v>
@@ -2251,103 +2253,103 @@
         <v>8</v>
       </c>
       <c r="F88" t="s">
-        <v>77</v>
+        <v>21</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="A89" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B89" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C89" s="2">
-        <v>38639</v>
+        <v>40491</v>
       </c>
       <c r="D89" t="s">
         <v>7</v>
       </c>
       <c r="E89" t="s">
         <v>8</v>
-      </c>
-      <c r="F89" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="90" spans="1:6">
       <c r="A90" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B90" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C90" s="2">
-        <v>45553</v>
+        <v>40084</v>
       </c>
       <c r="D90" t="s">
-        <v>44</v>
-      </c>
-      <c r="E90" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91" spans="1:6">
       <c r="A91" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B91" t="s">
-        <v>154</v>
+        <v>125</v>
       </c>
       <c r="C91" s="2">
-        <v>39724</v>
+        <v>40844</v>
       </c>
       <c r="D91" t="s">
         <v>7</v>
+      </c>
+      <c r="E91" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="92" spans="1:6">
       <c r="A92" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B92" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C92" s="2">
-        <v>39107</v>
+        <v>40458</v>
       </c>
       <c r="D92" t="s">
         <v>7</v>
       </c>
       <c r="E92" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="93" spans="1:6">
       <c r="A93" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B93" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C93" s="2">
-        <v>40458</v>
+        <v>40085</v>
       </c>
       <c r="D93" t="s">
         <v>7</v>
       </c>
       <c r="E93" t="s">
         <v>8</v>
+      </c>
+      <c r="F93" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="A94" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B94" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C94" s="2">
-        <v>39331</v>
+        <v>38639</v>
       </c>
       <c r="D94" t="s">
         <v>7</v>
@@ -2356,46 +2358,52 @@
         <v>8</v>
       </c>
       <c r="F94" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="95" spans="1:6">
       <c r="A95" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B95" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="C95" s="2">
-        <v>38686</v>
+        <v>46057</v>
       </c>
       <c r="D95" t="s">
-        <v>7</v>
+        <v>146</v>
+      </c>
+      <c r="E95" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="96" spans="1:6">
       <c r="A96" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B96" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C96" s="2">
-        <v>39167</v>
+        <v>45553</v>
       </c>
       <c r="D96" t="s">
-        <v>7</v>
+        <v>44</v>
+      </c>
+      <c r="E96" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B97" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="C97" s="2">
-        <v>39412</v>
+        <v>39724</v>
       </c>
       <c r="D97" t="s">
         <v>7</v>
@@ -2406,24 +2414,27 @@
         <v>22</v>
       </c>
       <c r="B98" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C98" s="2">
-        <v>40063</v>
+        <v>39107</v>
       </c>
       <c r="D98" t="s">
         <v>7</v>
+      </c>
+      <c r="E98" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B99" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C99" s="2">
-        <v>38863</v>
+        <v>40458</v>
       </c>
       <c r="D99" t="s">
         <v>7</v>
@@ -2437,30 +2448,30 @@
         <v>17</v>
       </c>
       <c r="B100" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C100" s="2">
-        <v>39513</v>
+        <v>39331</v>
       </c>
       <c r="D100" t="s">
         <v>7</v>
       </c>
       <c r="E100" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F100" t="s">
-        <v>139</v>
+        <v>28</v>
       </c>
     </row>
     <row r="101" spans="1:6">
       <c r="A101" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B101" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C101" s="2">
-        <v>39398</v>
+        <v>38686</v>
       </c>
       <c r="D101" t="s">
         <v>7</v>
@@ -2468,30 +2479,27 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" t="s">
-        <v>9</v>
+        <v>103</v>
       </c>
       <c r="B102" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="C102" s="2">
-        <v>39106</v>
+        <v>38686</v>
       </c>
       <c r="D102" t="s">
         <v>7</v>
-      </c>
-      <c r="E102" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="103" spans="1:6">
       <c r="A103" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B103" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="C103" s="2">
-        <v>40063</v>
+        <v>39167</v>
       </c>
       <c r="D103" t="s">
         <v>7</v>
@@ -2502,132 +2510,123 @@
         <v>9</v>
       </c>
       <c r="B104" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="C104" s="2">
-        <v>40220</v>
+        <v>39412</v>
       </c>
       <c r="D104" t="s">
         <v>7</v>
-      </c>
-      <c r="E104" t="s">
-        <v>8</v>
-      </c>
-      <c r="F104" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="105" spans="1:6">
       <c r="A105" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="B105" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="C105" s="2">
-        <v>45931</v>
+        <v>40063</v>
       </c>
       <c r="D105" t="s">
-        <v>44</v>
-      </c>
-      <c r="E105" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106" spans="1:6">
       <c r="A106" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B106" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C106" s="2">
-        <v>46057</v>
+        <v>38863</v>
       </c>
       <c r="D106" t="s">
-        <v>146</v>
+        <v>7</v>
       </c>
       <c r="E106" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
     </row>
     <row r="107" spans="1:6">
       <c r="A107" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B107" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C107" s="2">
-        <v>45687</v>
+        <v>39513</v>
       </c>
       <c r="D107" t="s">
+        <v>7</v>
+      </c>
+      <c r="E107" t="s">
+        <v>15</v>
+      </c>
+      <c r="F107" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="A108" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C108" s="5">
+        <v>45523</v>
+      </c>
+      <c r="D108" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E107" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6">
-      <c r="A108" t="s">
-        <v>17</v>
-      </c>
-      <c r="B108" t="s">
-        <v>148</v>
-      </c>
-      <c r="C108" s="2">
-        <v>45167</v>
-      </c>
-      <c r="D108" t="s">
-        <v>44</v>
-      </c>
-      <c r="E108" t="s">
+      <c r="E108" s="4" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="B109" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="C109" s="2">
-        <v>45523</v>
+        <v>39398</v>
       </c>
       <c r="D109" t="s">
-        <v>44</v>
-      </c>
-      <c r="E109" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
     </row>
     <row r="110" spans="1:6">
       <c r="A110" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B110" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="C110" s="2">
-        <v>45523</v>
+        <v>39106</v>
       </c>
       <c r="D110" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="E110" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
     </row>
     <row r="111" spans="1:6">
       <c r="A111" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B111" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="C111" s="2">
-        <v>39363</v>
+        <v>40063</v>
       </c>
       <c r="D111" t="s">
         <v>7</v>
@@ -2638,30 +2637,42 @@
         <v>9</v>
       </c>
       <c r="B112" t="s">
-        <v>18</v>
+        <v>143</v>
       </c>
       <c r="C112" s="2">
-        <v>39244</v>
+        <v>40220</v>
       </c>
       <c r="D112" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="113" spans="1:4">
+      <c r="E112" t="s">
+        <v>8</v>
+      </c>
+      <c r="F112" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
       <c r="A113" t="s">
-        <v>103</v>
+        <v>5</v>
       </c>
       <c r="B113" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="C113" s="2">
-        <v>38686</v>
+        <v>45931</v>
       </c>
       <c r="D113" t="s">
-        <v>7</v>
+        <v>44</v>
+      </c>
+      <c r="E113" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F113">
+    <sortCondition ref="B2:B113"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/sinodalias.xlsx
+++ b/sinodalias.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ildeberto/Desktop/Recopilacion/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ildeberto/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ADD584C-8F6B-694E-8DDD-612934F84CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C277217-B95A-1A47-B991-E90F03EA2F89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="36000" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="159">
   <si>
     <t>FUNCIÓN</t>
   </si>
@@ -488,6 +488,15 @@
   </si>
   <si>
     <t>NOMBRE DEL SUSTENTANTE</t>
+  </si>
+  <si>
+    <t>ESVAN DE JESUS PEREZ PEREZ</t>
+  </si>
+  <si>
+    <t>10/11/2023</t>
+  </si>
+  <si>
+    <t>FAULT DIAGNOSIS IN WIND TURBINES USING MACHINE LEARNING TECHNIQUES</t>
   </si>
 </sst>
 </file>
@@ -534,7 +543,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -543,6 +552,9 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -709,8 +721,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G113"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <dimension ref="A1:G114"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="40.83203125" customWidth="1"/>
@@ -2652,7 +2664,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="113" spans="1:5">
+    <row r="113" spans="1:6">
       <c r="A113" t="s">
         <v>5</v>
       </c>
@@ -2667,6 +2679,26 @@
       </c>
       <c r="E113" t="s">
         <v>45</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="A114" t="s">
+        <v>17</v>
+      </c>
+      <c r="B114" t="s">
+        <v>156</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="D114" t="s">
+        <v>146</v>
+      </c>
+      <c r="E114" t="s">
+        <v>45</v>
+      </c>
+      <c r="F114" t="s">
+        <v>158</v>
       </c>
     </row>
   </sheetData>

--- a/sinodalias.xlsx
+++ b/sinodalias.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ildeberto/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ildeberto/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C277217-B95A-1A47-B991-E90F03EA2F89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13B659A0-A6E4-C444-AF49-82CB0E21A79D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="36000" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="520" windowWidth="25600" windowHeight="14560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Jurado" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="162">
   <si>
     <t>FUNCIÓN</t>
   </si>
@@ -497,6 +497,15 @@
   </si>
   <si>
     <t>FAULT DIAGNOSIS IN WIND TURBINES USING MACHINE LEARNING TECHNIQUES</t>
+  </si>
+  <si>
+    <t>JAIME JIMENEZ PEREZ</t>
+  </si>
+  <si>
+    <t>05/06/2026</t>
+  </si>
+  <si>
+    <t>DIAGNÓSTICO DE FALLAS BASADO EN MODELOS QLPV PARA UN VANT TIPO QUADROTOR</t>
   </si>
 </sst>
 </file>
@@ -721,7 +730,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G115"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
@@ -2701,6 +2710,26 @@
         <v>158</v>
       </c>
     </row>
+    <row r="115" spans="1:6">
+      <c r="A115" t="s">
+        <v>17</v>
+      </c>
+      <c r="B115" t="s">
+        <v>159</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="D115" t="s">
+        <v>44</v>
+      </c>
+      <c r="E115" t="s">
+        <v>45</v>
+      </c>
+      <c r="F115" t="s">
+        <v>161</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F113">
     <sortCondition ref="B2:B113"/>
